--- a/doc/计划.xlsx
+++ b/doc/计划.xlsx
@@ -137,13 +137,13 @@
     <t>LCEL 与 Runnable 协议</t>
   </si>
   <si>
-    <t>用 LCEL 重写第一阶段的脚本，并加上流式输出（chain.stream）</t>
+    <t>一个用 LCEL 构建的、带结构化输出的命令行 Agent</t>
   </si>
   <si>
     <t> 模型 I/O 与提示词</t>
   </si>
   <si>
-    <t>一个用 LCEL 构建的、带结构化输出和工具调用能力的命令行 Agent</t>
+    <t>在基础上加上工具调用,并完善sys prompt</t>
   </si>
   <si>
     <t>RAG</t>
@@ -1503,6 +1503,7 @@
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="27.5357142857143" style="17" customWidth="1"/>
     <col min="4" max="4" width="74.7767857142857" style="16" customWidth="1"/>
+    <col min="5" max="5" width="29.7678571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.6" spans="1:4">

--- a/doc/计划.xlsx
+++ b/doc/计划.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
   <si>
     <t>1. 主流 Agent 框架掌握</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>运行本地向量库(Chroma 或 FAISS) 并读写数据</t>
+  </si>
+  <si>
+    <t>demo/rag/chroma_rag.py</t>
   </si>
   <si>
     <t>Naive RAG 到 Hybrid Retrieval</t>
@@ -954,7 +957,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1023,6 +1026,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1379,113 +1385,113 @@
   </cols>
   <sheetData>
     <row r="2" ht="34" spans="1:4">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="31" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:4">
-      <c r="A3" s="30"/>
-      <c r="B3" s="30" t="s">
+      <c r="A3" s="31"/>
+      <c r="B3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="31" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:4">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31" t="s">
+      <c r="A4" s="31"/>
+      <c r="B4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="31" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:4">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30" t="s">
+      <c r="A5" s="31"/>
+      <c r="B5" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="31" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="32"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
     </row>
     <row r="8" ht="55.2" customHeight="1" spans="1:4">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="41.4" customHeight="1" spans="1:4">
-      <c r="A9" s="30"/>
-      <c r="B9" s="30" t="s">
+      <c r="A9" s="31"/>
+      <c r="B9" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="31" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" ht="27.6" customHeight="1" spans="1:4">
-      <c r="A10" s="30"/>
-      <c r="B10" s="30" t="s">
+      <c r="A10" s="31"/>
+      <c r="B10" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="31" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" ht="41.4" customHeight="1" spans="1:4">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30" t="s">
+      <c r="A11" s="31"/>
+      <c r="B11" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="31" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" ht="41.4" customHeight="1" spans="1:4">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30" t="s">
+      <c r="A12" s="31"/>
+      <c r="B12" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="31" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="33"/>
+      <c r="A16" s="34"/>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="33"/>
+      <c r="A19" s="34"/>
     </row>
     <row r="20" spans="1:2">
-      <c r="B20" s="33"/>
+      <c r="B20" s="34"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="33"/>
+      <c r="A22" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1496,8 +1502,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="23.9464285714286" style="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1506,7 +1512,7 @@
     <col min="5" max="5" width="29.7678571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.6" spans="1:4">
+    <row r="1" ht="17.6" spans="1:5">
       <c r="A1" s="18" t="s">
         <v>20</v>
       </c>
@@ -1518,7 +1524,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" ht="18" spans="1:4">
+    <row r="2" ht="18" spans="1:5">
       <c r="A2" s="18" t="s">
         <v>23</v>
       </c>
@@ -1532,7 +1538,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" ht="18" spans="1:4">
+    <row r="3" ht="18" spans="1:5">
       <c r="A3" s="18"/>
       <c r="B3" s="19">
         <v>261020</v>
@@ -1544,7 +1550,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" ht="18" spans="1:4">
+    <row r="4" ht="18" spans="1:5">
       <c r="A4" s="18"/>
       <c r="B4" s="19">
         <v>261021</v>
@@ -1554,7 +1560,7 @@
       </c>
       <c r="D4" s="22"/>
     </row>
-    <row r="5" ht="18" spans="1:4">
+    <row r="5" ht="18" spans="1:5">
       <c r="A5" s="18" t="s">
         <v>28</v>
       </c>
@@ -1568,7 +1574,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" ht="18" spans="1:4">
+    <row r="6" ht="18" spans="1:5">
       <c r="A6" s="18"/>
       <c r="B6" s="19">
         <v>261023</v>
@@ -1578,7 +1584,7 @@
       </c>
       <c r="D6" s="23"/>
     </row>
-    <row r="7" ht="18" spans="1:4">
+    <row r="7" ht="18" spans="1:5">
       <c r="A7" s="18" t="s">
         <v>31</v>
       </c>
@@ -1592,7 +1598,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" ht="18" spans="1:4">
+    <row r="8" ht="18" spans="1:5">
       <c r="A8" s="18"/>
       <c r="B8" s="19">
         <v>261027</v>
@@ -1604,7 +1610,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" ht="18" spans="1:4">
+    <row r="9" ht="18" spans="1:5">
       <c r="A9" s="18"/>
       <c r="B9" s="19">
         <v>261028</v>
@@ -1616,7 +1622,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" ht="36" spans="1:4">
+    <row r="10" ht="36" spans="1:5">
       <c r="A10" s="24" t="s">
         <v>38</v>
       </c>
@@ -1629,72 +1635,77 @@
       <c r="D10" s="22" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" ht="36" spans="1:4">
+      <c r="E10" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" ht="36" spans="1:5">
       <c r="A11" s="24"/>
       <c r="B11" s="19">
         <v>261030</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" ht="18" spans="1:4">
+        <v>43</v>
+      </c>
+      <c r="E11" s="25"/>
+    </row>
+    <row r="12" ht="18" spans="1:5">
       <c r="A12" s="24"/>
       <c r="B12" s="19">
         <v>261102</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" s="22"/>
-    </row>
-    <row r="13" ht="18" spans="1:4">
+      <c r="E12" s="25"/>
+    </row>
+    <row r="13" ht="18" spans="1:5">
       <c r="A13" s="18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="19">
         <v>261103</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" ht="18" spans="1:4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" ht="18" spans="1:5">
       <c r="A14" s="18"/>
       <c r="B14" s="19"/>
-      <c r="C14" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="26" t="s">
+      <c r="C14" s="26" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" ht="17.6" spans="1:4">
+      <c r="D14" s="27" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" ht="17.6" spans="1:5">
       <c r="A15" s="18"/>
       <c r="B15" s="19">
         <v>261104</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="26" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" ht="17.6" spans="1:4">
+      <c r="D15" s="27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" ht="17.6" spans="1:5">
       <c r="A16" s="18"/>
       <c r="B16" s="19">
         <v>261105</v>
       </c>
       <c r="C16" s="20"/>
-      <c r="D16" s="26"/>
+      <c r="D16" s="27"/>
     </row>
     <row r="17" ht="17.6" spans="1:4">
       <c r="A17" s="18"/>
@@ -1702,10 +1713,10 @@
         <v>261106</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="26" t="s">
         <v>52</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="18" ht="17.6" spans="1:4">
@@ -1714,7 +1725,7 @@
         <v>261109</v>
       </c>
       <c r="C18" s="24"/>
-      <c r="D18" s="26"/>
+      <c r="D18" s="27"/>
     </row>
     <row r="19" ht="18" spans="1:4">
       <c r="A19" s="18"/>
@@ -1722,28 +1733,28 @@
         <v>261110</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="26" t="s">
         <v>54</v>
       </c>
+      <c r="D19" s="27" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="20" ht="17.6" spans="1:4">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="27"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="28"/>
     </row>
     <row r="21" ht="17.6" spans="1:4">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="27"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A9"/>
@@ -1757,6 +1768,7 @@
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E10:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1777,21 +1789,21 @@
     <row r="1" spans="1:3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="3"/>
@@ -1802,13 +1814,13 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" s="10"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" s="12"/>
     </row>
@@ -1826,7 +1838,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="12"/>
     </row>
@@ -1844,7 +1856,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" s="13"/>
     </row>
@@ -1854,7 +1866,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="13"/>
     </row>
@@ -1864,7 +1876,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" s="13"/>
     </row>
@@ -1914,43 +1926,43 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="B2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" t="s">
         <v>71</v>
-      </c>
-      <c r="J3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="B4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:10">
